--- a/public/exports-with-coowners/29189633.xlsx
+++ b/public/exports-with-coowners/29189633.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -3139,7 +3139,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t xml:space="preserve">311366596</t>
+          <t xml:space="preserve">311366598</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3214,7 +3214,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t xml:space="preserve">311366589</t>
+          <t xml:space="preserve">311366590</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -5839,7 +5839,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t xml:space="preserve">311379031</t>
+          <t xml:space="preserve">311379034</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -6064,7 +6064,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t xml:space="preserve">311379054</t>
+          <t xml:space="preserve">311379055</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -8089,7 +8089,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t xml:space="preserve">311381685</t>
+          <t xml:space="preserve">311381687</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">

--- a/public/exports-with-coowners/29189633.xlsx
+++ b/public/exports-with-coowners/29189633.xlsx
@@ -3139,7 +3139,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t xml:space="preserve">311366598</t>
+          <t xml:space="preserve">311366599</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3214,7 +3214,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t xml:space="preserve">311366590</t>
+          <t xml:space="preserve">311366591</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -5914,7 +5914,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t xml:space="preserve">311379064</t>
+          <t xml:space="preserve">311379069</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5989,7 +5989,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t xml:space="preserve">311379047</t>
+          <t xml:space="preserve">311379050</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -6064,7 +6064,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t xml:space="preserve">311379055</t>
+          <t xml:space="preserve">311379059</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -8089,7 +8089,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t xml:space="preserve">311381687</t>
+          <t xml:space="preserve">311381685</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -17239,7 +17239,7 @@
       </c>
       <c r="K230" t="inlineStr">
         <is>
-          <t xml:space="preserve">311422167</t>
+          <t xml:space="preserve">311422168</t>
         </is>
       </c>
       <c r="L230" t="inlineStr">

--- a/public/exports-with-coowners/29189633.xlsx
+++ b/public/exports-with-coowners/29189633.xlsx
@@ -3214,7 +3214,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t xml:space="preserve">311366591</t>
+          <t xml:space="preserve">311366589</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -17239,7 +17239,7 @@
       </c>
       <c r="K230" t="inlineStr">
         <is>
-          <t xml:space="preserve">311422168</t>
+          <t xml:space="preserve">311422167</t>
         </is>
       </c>
       <c r="L230" t="inlineStr">
